--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487986_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487986_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.5984</v>
+        <v>8.1381</v>
       </c>
       <c r="E2" t="n">
-        <v>4.2173</v>
+        <v>4.2797</v>
       </c>
       <c r="F2" t="n">
-        <v>3.3811</v>
+        <v>3.8584</v>
       </c>
       <c r="G2" t="n">
         <v>4.9143</v>
@@ -610,13 +610,13 @@
         <v>2.1805</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1421</v>
+        <v>0.6818</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6719000000000001</v>
+        <v>0.7343</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5298</v>
+        <v>-0.0525</v>
       </c>
       <c r="V2" t="n">
         <v>2.3438</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.8982</v>
+        <v>7.7371</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4435</v>
+        <v>4.4227</v>
       </c>
       <c r="F3" t="n">
-        <v>3.4547</v>
+        <v>3.3143</v>
       </c>
       <c r="G3" t="n">
         <v>3.0979</v>
@@ -688,13 +688,13 @@
         <v>2.5769</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0164</v>
+        <v>0.8552</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8736</v>
+        <v>0.1057</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8899</v>
+        <v>0.7495000000000001</v>
       </c>
       <c r="V3" t="n">
         <v>1.2071</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.238</v>
+        <v>4.0102</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07480000000000001</v>
+        <v>1.1559</v>
       </c>
       <c r="F4" t="n">
-        <v>3.1632</v>
+        <v>2.8543</v>
       </c>
       <c r="G4" t="n">
         <v>6.283</v>
@@ -766,13 +766,13 @@
         <v>2.7751</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1401</v>
+        <v>0.6322</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9984</v>
+        <v>0.0827</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8583</v>
+        <v>0.5494</v>
       </c>
       <c r="V4" t="n">
         <v>0.2666</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. ESPINAL REYNOSO</t>
+          <t>J. MORALES MUÑOZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5021</v>
+        <v>0.3027</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.9708</v>
+        <v>0.3027</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4729</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>2.1902</v>
+        <v>0.3027</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9966</v>
+        <v>0.3027</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1937</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1.8569</v>
+        <v>0.3027</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9691</v>
+        <v>0.3027</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8878</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3333</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0275</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3059</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.9645</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.9733</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.7876</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.1477</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6399</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.4846</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-1.0109</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.4737</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. MORALES MUÑOZ</t>
+          <t>J. MARTINEZ GUZMAN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3027</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3027</v>
+        <v>-0.1461</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>0.0592</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3027</v>
+        <v>-0.3815</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3027</v>
+        <v>0.2461</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>-0.6274999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3027</v>
+        <v>-0.5986</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3027</v>
+        <v>0.0404</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0.639</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>0.2171</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>0.2057</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.0114</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.1982</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>0.1982</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>0.0964</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.4525</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>-0.3561</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. MARTINEZ GUZMAN</t>
+          <t>J. ESPINAL REYNOSO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0974</v>
+        <v>-0.132</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0443</v>
+        <v>-2.4365</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0531</v>
+        <v>2.3044</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3815</v>
+        <v>2.1902</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2461</v>
+        <v>0.9966</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6274999999999999</v>
+        <v>1.1937</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.5986</v>
+        <v>1.8569</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0404</v>
+        <v>0.9691</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.639</v>
+        <v>0.8878</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2171</v>
+        <v>0.3333</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2057</v>
+        <v>0.0275</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0114</v>
+        <v>0.3059</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1982</v>
+        <v>-0.9911</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-3.9645</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1982</v>
+        <v>2.9733</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0859</v>
+        <v>1.1535</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5543</v>
+        <v>0.6821</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4684</v>
+        <v>0.4714</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-2.4846</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-1.0109</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1231</v>
+        <v>-0.4859</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.3781</v>
+        <v>-2.8251</v>
       </c>
       <c r="F8" t="n">
-        <v>2.255</v>
+        <v>2.3392</v>
       </c>
       <c r="G8" t="n">
         <v>-2.4977</v>
@@ -1078,13 +1078,13 @@
         <v>2.1805</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7977</v>
+        <v>0.435</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4223</v>
+        <v>-0.0246</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3754</v>
+        <v>0.4596</v>
       </c>
       <c r="V8" t="n">
         <v>-0.6036</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7136</v>
+        <v>-0.5732</v>
       </c>
       <c r="E9" t="n">
         <v>0.3315</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.045</v>
+        <v>-0.9046</v>
       </c>
       <c r="G9" t="n">
         <v>-0.5576</v>
@@ -1156,13 +1156,13 @@
         <v>0.3964</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5524</v>
+        <v>-0.412</v>
       </c>
       <c r="T9" t="n">
         <v>-0.3744</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1781</v>
+        <v>-0.0377</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.7993</v>
+        <v>-3.6693</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.3807</v>
+        <v>-2.2788</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4186</v>
+        <v>-1.3905</v>
       </c>
       <c r="G10" t="n">
         <v>-0.6911</v>
@@ -1234,13 +1234,13 @@
         <v>0.7929</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7118</v>
+        <v>-0.5818</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4992</v>
+        <v>-0.3973</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2126</v>
+        <v>-0.1845</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2071</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.6775</v>
+        <v>-6.8003</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.3896</v>
+        <v>-6.2878</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2879</v>
+        <v>-0.5125</v>
       </c>
       <c r="G11" t="n">
         <v>-2.5302</v>
@@ -1312,13 +1312,13 @@
         <v>0.7929</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0154</v>
+        <v>-0.1074</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4992</v>
+        <v>-0.3973</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5145999999999999</v>
+        <v>0.2899</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>8.128499999999999</v>
+        <v>8.4405</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.793699999999999</v>
+        <v>-3.481799999999998</v>
       </c>
       <c r="F12" t="n">
-        <v>11.9223</v>
+        <v>11.9222</v>
       </c>
       <c r="G12" t="n">
         <v>10.13</v>
@@ -1366,16 +1366,16 @@
         <v>10.4722</v>
       </c>
       <c r="K12" t="n">
-        <v>7.333100000000001</v>
+        <v>7.3331</v>
       </c>
       <c r="L12" t="n">
         <v>3.1391</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.3422000000000001</v>
+        <v>-0.3421999999999996</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1375000000000002</v>
+        <v>0.1375</v>
       </c>
       <c r="O12" t="n">
         <v>-0.4795000000000001</v>
@@ -1390,16 +1390,16 @@
         <v>14.8667</v>
       </c>
       <c r="S12" t="n">
-        <v>2.4408</v>
+        <v>2.7529</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5514000000000002</v>
+        <v>0.8637000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>1.8892</v>
+        <v>1.889</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.4778000000000001</v>
+        <v>-0.4778000000000002</v>
       </c>
       <c r="W12" t="n">
         <v>4.0137</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.3875</v>
+        <v>4.1099</v>
       </c>
       <c r="E13" t="n">
-        <v>2.8489</v>
+        <v>2.5433</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5386</v>
+        <v>1.5666</v>
       </c>
       <c r="G13" t="n">
         <v>2.9077</v>
@@ -1468,13 +1468,13 @@
         <v>0.5947</v>
       </c>
       <c r="S13" t="n">
-        <v>0.885</v>
+        <v>0.6075</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5543</v>
+        <v>0.2487</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3307</v>
+        <v>0.3588</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.9435</v>
+        <v>2.8455</v>
       </c>
       <c r="E14" t="n">
-        <v>2.394</v>
+        <v>2.8015</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5495</v>
+        <v>0.0441</v>
       </c>
       <c r="G14" t="n">
         <v>3.2799</v>
@@ -1546,13 +1546,13 @@
         <v>3.3698</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5169</v>
+        <v>-0.6148</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.068</v>
+        <v>-0.6605</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5511</v>
+        <v>0.0457</v>
       </c>
       <c r="V14" t="n">
         <v>-1.2071</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E. LALI VICENTE UCHUATE</t>
+          <t>A. GARCIA MONTELLANO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8427</v>
+        <v>1.0848</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.009599999999999999</v>
+        <v>1.4713</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8523</v>
+        <v>-0.3865</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.0521</v>
+        <v>-2.1273</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.2962</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.7559</v>
+        <v>-2.2041</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.6118</v>
+        <v>-0.8945</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.0934</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5184</v>
+        <v>-1.8365</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.4403</v>
+        <v>-1.2328</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.2028</v>
+        <v>-0.8652</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.2374</v>
+        <v>-0.3676</v>
       </c>
       <c r="P15" t="n">
-        <v>2.9733</v>
+        <v>2.3787</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.9733</v>
+        <v>2.3787</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9215</v>
+        <v>-0.4441</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6022999999999999</v>
+        <v>-0.0484</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3192</v>
+        <v>-0.3957</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.2775</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.4142</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.1367</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. GARCIA MONTELLANO</t>
+          <t>E. LALI VICENTE UCHUATE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.7137</v>
+        <v>1.0278</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1844</v>
+        <v>-0.8245</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4707</v>
+        <v>1.8523</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.1273</v>
+        <v>-2.0521</v>
       </c>
       <c r="H16" t="n">
-        <v>0.07679999999999999</v>
+        <v>-1.2962</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.2041</v>
+        <v>-0.7559</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.8945</v>
+        <v>-0.6118</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9419999999999999</v>
+        <v>-0.0934</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.8365</v>
+        <v>-0.5184</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.2328</v>
+        <v>-1.4403</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8652</v>
+        <v>-1.2028</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.3676</v>
+        <v>-0.2374</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3787</v>
+        <v>2.9733</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3787</v>
+        <v>2.9733</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1847</v>
+        <v>0.1065</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6647</v>
+        <v>-0.2127</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4799</v>
+        <v>0.3192</v>
       </c>
       <c r="V16" t="n">
-        <v>1.2775</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.4142</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.1367</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3138</v>
+        <v>-0.2577</v>
       </c>
       <c r="E17" t="n">
         <v>-1.4862</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1724</v>
+        <v>1.2285</v>
       </c>
       <c r="G17" t="n">
         <v>0.6229</v>
@@ -1780,13 +1780,13 @@
         <v>0.7929</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4214</v>
+        <v>-0.3652</v>
       </c>
       <c r="T17" t="n">
         <v>-0.1872</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2342</v>
+        <v>-0.1781</v>
       </c>
       <c r="V17" t="n">
         <v>0.674</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0809</v>
+        <v>-1.0424</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.9983</v>
+        <v>-2.1002</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9174</v>
+        <v>1.0578</v>
       </c>
       <c r="G18" t="n">
         <v>-0.8421</v>
@@ -1858,13 +1858,13 @@
         <v>1.9822</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1488</v>
+        <v>0.1873</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0479</v>
+        <v>-0.054</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1008</v>
+        <v>0.2412</v>
       </c>
       <c r="V18" t="n">
         <v>0.6036</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.4123</v>
+        <v>-2.089</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.7238</v>
+        <v>-2.3163</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3115</v>
+        <v>0.2273</v>
       </c>
       <c r="G19" t="n">
         <v>-1.5522</v>
@@ -1936,13 +1936,13 @@
         <v>0.7929</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6619</v>
+        <v>-0.3386</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3744</v>
+        <v>0.0331</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2875</v>
+        <v>-0.3717</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>F. GARCIA GARRIDO</t>
+          <t>J. REVUELTAS PAREJA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.7968</v>
+        <v>-2.6573</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.7862</v>
+        <v>-2.2583</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0107</v>
+        <v>-0.399</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.1486</v>
+        <v>-2.3459</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.2845</v>
+        <v>-1.5615</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1358</v>
+        <v>-0.7844</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6791</v>
+        <v>-0.8864</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6791</v>
+        <v>-0.8942</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>0.0078</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4695</v>
+        <v>-1.4595</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6052999999999999</v>
+        <v>-0.6674</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1358</v>
+        <v>-0.7922</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.3876</v>
+        <v>0.9911</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="R20" t="n">
-        <v>0.5947</v>
+        <v>1.9822</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2606</v>
+        <v>-0.0954</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1248</v>
+        <v>-0.3808</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1358</v>
+        <v>0.2854</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. REVUELTAS PAREJA</t>
+          <t>F. GARCIA GARRIDO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.2156</v>
+        <v>-2.7968</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.5639</v>
+        <v>-2.7862</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6516999999999999</v>
+        <v>-0.0107</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.3459</v>
+        <v>-1.1486</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.5615</v>
+        <v>-1.2845</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7844</v>
+        <v>0.1358</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.8864</v>
+        <v>-0.6791</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.8942</v>
+        <v>-0.6791</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0078</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.4595</v>
+        <v>-0.4695</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6674</v>
+        <v>-0.6052999999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.7922</v>
+        <v>0.1358</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9911</v>
+        <v>-1.3876</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R21" t="n">
-        <v>1.9822</v>
+        <v>0.5947</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6536999999999999</v>
+        <v>-0.2606</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6864</v>
+        <v>-0.1248</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0326</v>
+        <v>-0.1358</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.8947</v>
+        <v>-3.5996</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.6662</v>
+        <v>-2.2587</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.2285</v>
+        <v>-1.3408</v>
       </c>
       <c r="G22" t="n">
         <v>-3.375</v>
@@ -2170,13 +2170,13 @@
         <v>2.1805</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.055</v>
+        <v>-0.7598</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.756</v>
+        <v>-0.3485</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.299</v>
+        <v>-0.4113</v>
       </c>
       <c r="V22" t="n">
         <v>0.337</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.3016</v>
+        <v>-4.7537</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.1154</v>
+        <v>-4.7079</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1862</v>
+        <v>-0.0458</v>
       </c>
       <c r="G23" t="n">
         <v>-3.4974</v>
@@ -2248,13 +2248,13 @@
         <v>1.1893</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0113</v>
+        <v>-0.4634</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5616</v>
+        <v>-0.1541</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4497</v>
+        <v>-0.3093</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-8.128299999999999</v>
+        <v>-8.128500000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>-11.9223</v>
+        <v>-11.9222</v>
       </c>
       <c r="F24" t="n">
-        <v>3.793900000000001</v>
+        <v>3.793800000000001</v>
       </c>
       <c r="G24" t="n">
         <v>-10.1301</v>
@@ -2311,7 +2311,7 @@
         <v>-10.4721</v>
       </c>
       <c r="N24" t="n">
-        <v>-7.333099999999999</v>
+        <v>-7.3331</v>
       </c>
       <c r="O24" t="n">
         <v>-3.1391</v>
@@ -2326,13 +2326,13 @@
         <v>18.8312</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.4408</v>
+        <v>-2.4406</v>
       </c>
       <c r="T24" t="n">
         <v>-1.8892</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5516999999999999</v>
+        <v>-0.5516</v>
       </c>
       <c r="V24" t="n">
         <v>0.4779</v>
